--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8C877C-4644-47C5-B0B0-8809F61F19B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB83B3D8-C61B-4C90-BF58-F2D79A4FD05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35715" yWindow="2805" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -199,34 +199,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Attack Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack Range</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Projectile Speed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Build Cost</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Price</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Upgrade Id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Upgrade Cost</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -243,19 +215,51 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Attack Speed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Move Type</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Ground</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ground, Sky</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackDamage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileSpeed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildPrice</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SellPrice</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradePrice</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ddd</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -726,31 +730,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -759,31 +763,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="H3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="I3" s="14" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K3" s="11"/>
     </row>
@@ -804,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1">
         <v>50</v>
@@ -812,7 +816,9 @@
       <c r="H4" s="1">
         <v>25</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="J4" s="1">
         <v>45</v>
       </c>
@@ -839,7 +845,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
         <v>75</v>
@@ -847,7 +853,9 @@
       <c r="H5" s="1">
         <v>50</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="J5" s="1">
         <v>60</v>
       </c>

--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB83B3D8-C61B-4C90-BF58-F2D79A4FD05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DF5637-A7E0-4BF2-A3B9-FD42F5A8B409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35715" yWindow="2805" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -261,6 +261,21 @@
   <si>
     <t>ddd</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PrefabPath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리팹 주소</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Tower/tower_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Tower/tower_02</t>
   </si>
 </sst>
 </file>
@@ -689,7 +704,8 @@
     <col min="7" max="8" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="40" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.5703125" style="2"/>
+    <col min="11" max="11" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
@@ -723,7 +739,9 @@
       <c r="J1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="9"/>
+      <c r="K1" s="9" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="2" spans="1:15" ht="12.75">
       <c r="A2" s="1" t="s">
@@ -756,7 +774,9 @@
       <c r="J2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="9"/>
+      <c r="K2" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:15" s="12" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="10" t="s">
@@ -789,7 +809,9 @@
       <c r="J3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="11"/>
+      <c r="K3" s="11" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -822,7 +844,9 @@
       <c r="J4" s="1">
         <v>45</v>
       </c>
-      <c r="K4" s="9"/>
+      <c r="K4" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -859,7 +883,9 @@
       <c r="J5" s="1">
         <v>60</v>
       </c>
-      <c r="K5" s="9"/>
+      <c r="K5" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>

--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DF5637-A7E0-4BF2-A3B9-FD42F5A8B409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63C4F35-6371-47EC-863F-99F26FB9014E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
@@ -818,10 +818,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -857,13 +857,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="D5" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1">
         <v>10</v>

--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63C4F35-6371-47EC-863F-99F26FB9014E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC01FE3-8873-46D5-9203-179F38D6310B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3810" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -276,6 +276,14 @@
   </si>
   <si>
     <t>Prefab/Tower/tower_02</t>
+  </si>
+  <si>
+    <t>tower_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Tower/tower_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -439,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -474,6 +482,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -866,10 +875,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1">
         <v>75</v>
@@ -892,17 +901,39 @@
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="9"/>
+      <c r="A6" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
+        <v>50</v>
+      </c>
+      <c r="H6" s="1">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="1">
+        <v>45</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>

--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC01FE3-8873-46D5-9203-179F38D6310B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B60E7A-0140-4C30-BEF1-E686B8643930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -284,6 +284,12 @@
   <si>
     <t>Prefab/Tower/tower_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_04</t>
+  </si>
+  <si>
+    <t>Prefab/Tower/tower_04</t>
   </si>
 </sst>
 </file>
@@ -914,7 +920,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>19</v>
@@ -940,17 +946,39 @@
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="9"/>
+      <c r="A7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="1">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>75</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="1">
+        <v>45</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>

--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B60E7A-0140-4C30-BEF1-E686B8643930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09781A3-2BA6-4145-9796-B0CE8AB36493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="2070" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -290,6 +290,12 @@
   </si>
   <si>
     <t>Prefab/Tower/tower_04</t>
+  </si>
+  <si>
+    <t>tower_05</t>
+  </si>
+  <si>
+    <t>Prefab/Tower/tower_05</t>
   </si>
 </sst>
 </file>
@@ -985,17 +991,39 @@
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="9"/>
+      <c r="A8" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="1">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>75</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="1">
+        <v>46</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>

--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09781A3-2BA6-4145-9796-B0CE8AB36493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E230F5F4-D250-4F5A-BFF3-272E51C05746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="2070" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3645" yWindow="2280" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -296,6 +296,12 @@
   </si>
   <si>
     <t>Prefab/Tower/tower_05</t>
+  </si>
+  <si>
+    <t>tower_06</t>
+  </si>
+  <si>
+    <t>Prefab/Tower/tower_06</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1007,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
         <v>7</v>
@@ -1030,17 +1036,39 @@
       <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="9"/>
+      <c r="A9" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="1">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1">
+        <v>75</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="1">
+        <v>47</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>

--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E230F5F4-D250-4F5A-BFF3-272E51C05746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B0AF8-6EEF-408B-B01E-3B5490300070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3645" yWindow="2280" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2865" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -207,10 +207,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>enum</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -219,10 +215,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Ground, Sky</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>AttackDamage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -302,6 +294,14 @@
   </si>
   <si>
     <t>Prefab/Tower/tower_06</t>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ground,Sky</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -767,7 +767,7 @@
         <v>13</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="12.75">
@@ -787,7 +787,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
@@ -796,13 +796,13 @@
         <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="12" customFormat="1" ht="15.75" customHeight="1">
@@ -810,34 +810,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="E3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="H3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="I3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="J3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="14" t="s">
+      <c r="K3" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1">
         <v>50</v>
@@ -866,13 +866,13 @@
         <v>25</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J4" s="1">
         <v>45</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1">
         <v>75</v>
@@ -905,13 +905,13 @@
         <v>50</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J5" s="1">
         <v>60</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -920,7 +920,7 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1">
         <v>6</v>
@@ -935,7 +935,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
         <v>50</v>
@@ -944,13 +944,13 @@
         <v>50</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J6" s="1">
         <v>45</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -959,7 +959,7 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G7" s="1">
         <v>100</v>
@@ -983,13 +983,13 @@
         <v>75</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J7" s="1">
         <v>45</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -998,7 +998,7 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -1013,7 +1013,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1">
         <v>100</v>
@@ -1022,13 +1022,13 @@
         <v>75</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J8" s="1">
         <v>46</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -1052,7 +1052,7 @@
         <v>7</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G9" s="1">
         <v>100</v>
@@ -1061,13 +1061,13 @@
         <v>75</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J9" s="1">
         <v>47</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
